--- a/nano_agent/agent/prompts.xlsx
+++ b/nano_agent/agent/prompts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,6 +451,16 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>是否稳定</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>模块分类</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>内容模板</t>
         </is>
       </c>
@@ -476,13 +486,28 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>You are an intelligent assistant that can use tools.
 ## Work Cycle
-Think -&gt; Act -&gt; Observe -&gt; Repeat until done.</t>
+Think -&gt; Act -&gt; Observe -&gt; Repeat until done.
+## Confidence Assessment
+After each thought, assess your confidence (0.0-1.0):
+- 0.9+: Can answer definitively without more tools
+- 0.7-0.9: Likely can answer, but may need verification
+- 0.5-0.7: Need more information
+- &lt;0.5: Significant uncertainty, must gather more data
+When confident (0.8+), provide your answer directly.</t>
         </is>
       </c>
     </row>
@@ -509,7 +534,15 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>## Tools
 {tools_description}</t>
@@ -539,7 +572,15 @@
       <c r="F4" t="n">
         <v>50</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>efficiency</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>## Efficiency Rules
 1. Minimize iterations (aim for 2-3)
@@ -572,7 +613,15 @@
       <c r="F5" t="n">
         <v>40</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>efficiency</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>## Modification Constraints
 1. Only modify what's relevant
@@ -605,7 +654,15 @@
       <c r="F6" t="n">
         <v>50</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>## Security Guidelines
 1. Assist security testing only with explicit authorization
@@ -637,7 +694,15 @@
       <c r="F7" t="n">
         <v>60</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>## Risk Awareness
 Before dangerous operations:
@@ -672,7 +737,15 @@
       <c r="F8" t="n">
         <v>50</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>## Security Rules
 Prevent vulnerabilities:
@@ -707,7 +780,15 @@
       <c r="F9" t="n">
         <v>30</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>## Output Style
 - No emojis unless requested
@@ -740,7 +821,15 @@
       <c r="F10" t="n">
         <v>10</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Respond in user's language.</t>
         </is>
@@ -769,7 +858,15 @@
       <c r="F11" t="n">
         <v>50</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -794,7 +891,15 @@
       <c r="F12" t="n">
         <v>80</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -819,7 +924,15 @@
       <c r="F13" t="n">
         <v>50</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>## Memory System
 Use `memorize` tool to store important information:
@@ -937,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,74 +1115,88 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>- content: 模块内容模板</t>
+          <t>- is_stable: 是否属于稳定部分(适合缓存)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>- category: 模块分类(core/efficiency/security/output/context/memory)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Styles 表:</t>
+          <t>- content: 模块内容模板</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>- style_name: 风格名称(concise/standard/detailed)</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- modules: 包含的模块列表(逗号分隔)</t>
+          <t>Styles 表:</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- token_budget: Token 预算上限</t>
+          <t>- style_name: 风格名称(concise/standard/detailed)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>- modules: 包含的模块列表(逗号分隔)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>使用方法:</t>
+          <t>- token_budget: Token 预算上限</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1. 修改 enabled 列来启用/禁用模块</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2. 修改 Styles 表中的 modules 列来调整各风格包含的模块</t>
+          <t>使用方法:</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3. 修改 content 列来调整模块内容</t>
+          <t>1. 修改 enabled 列来启用/禁用模块</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
+        <is>
+          <t>2. 修改 Styles 表中的 modules 列来调整各风格包含的模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3. 修改 content 列来调整模块内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>4. 修改 priority 列来调整模块顺序</t>
         </is>
